--- a/data/gravel/Tumbleweed Prospector 2025.xlsx
+++ b/data/gravel/Tumbleweed Prospector 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/hardtail/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A6F46F-1838-4D41-ADF5-16F7B1B5A567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5BF9199-23DC-AA49-BB97-78B3110E7B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="112">
   <si>
     <t>brand</t>
   </si>
@@ -1365,9 +1365,7 @@
       <c r="A44" t="s">
         <v>40</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>35</v>
-      </c>
+      <c r="B44" s="1"/>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">

--- a/data/gravel/Tumbleweed Prospector 2025.xlsx
+++ b/data/gravel/Tumbleweed Prospector 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5BF9199-23DC-AA49-BB97-78B3110E7B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7880E66D-BF9C-C94F-8E99-C768C52D45D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="113">
   <si>
     <t>brand</t>
   </si>
@@ -369,6 +369,9 @@
   </si>
   <si>
     <t>a8:f32</t>
+  </si>
+  <si>
+    <t>https://tumbleweed.cc/cdn/shop/files/pros-award_23a5939b-1eba-42bb-babf-7ffab42be634.jpg?v=1756404856&amp;width=1000</t>
   </si>
 </sst>
 </file>
@@ -784,6 +787,11 @@
         <v>102</v>
       </c>
     </row>
+    <row r="6" spans="1:11">
+      <c r="B6" t="s">
+        <v>112</v>
+      </c>
+    </row>
     <row r="7" spans="1:11" ht="22">
       <c r="A7" t="s">
         <v>6</v>

--- a/data/gravel/Tumbleweed Prospector 2025.xlsx
+++ b/data/gravel/Tumbleweed Prospector 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7880E66D-BF9C-C94F-8E99-C768C52D45D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B37A559-5B36-374E-9616-C21642240EC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="115">
   <si>
     <t>brand</t>
   </si>
@@ -281,9 +281,6 @@
     <t>no</t>
   </si>
   <si>
-    <t>us</t>
-  </si>
-  <si>
     <t>Tumbleweed</t>
   </si>
   <si>
@@ -372,6 +369,15 @@
   </si>
   <si>
     <t>https://tumbleweed.cc/cdn/shop/files/pros-award_23a5939b-1eba-42bb-babf-7ffab42be634.jpg?v=1756404856&amp;width=1000</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Garden City, Idaho, USA</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -741,7 +747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:K73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -752,7 +758,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -760,7 +766,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -784,12 +790,12 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="B6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="22">
@@ -797,7 +803,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C7" s="3"/>
     </row>
@@ -806,19 +812,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="21">
@@ -826,7 +832,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C9" s="6">
         <v>600</v>
@@ -846,7 +852,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C10" s="4">
         <f>H10*25.4</f>
@@ -882,7 +888,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C11" s="6">
         <v>69.5</v>
@@ -902,7 +908,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C12" s="6">
         <v>73</v>
@@ -922,7 +928,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C13" s="6">
         <v>58.5</v>
@@ -942,7 +948,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C14" s="6">
         <v>456</v>
@@ -962,7 +968,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C15" s="6">
         <v>110</v>
@@ -1082,7 +1088,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C21" s="6">
         <v>772</v>
@@ -1280,19 +1286,19 @@
         <v>70</v>
       </c>
       <c r="C35" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D35" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="E35" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="F35" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="F35" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="G35" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="21">
@@ -1300,22 +1306,22 @@
         <v>71</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C36" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D36" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D36" s="6" t="s">
+      <c r="E36" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E36" s="6" t="s">
+      <c r="F36" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="F36" s="6" t="s">
-        <v>101</v>
-      </c>
       <c r="G36" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1331,7 +1337,7 @@
         <v>33</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1567,7 +1573,15 @@
         <v>68</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>82</v>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Tumbleweed Prospector 2025.xlsx
+++ b/data/gravel/Tumbleweed Prospector 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B37A559-5B36-374E-9616-C21642240EC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6995A89-8D60-3847-8999-659B965234CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="116">
   <si>
     <t>brand</t>
   </si>
@@ -378,6 +378,9 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>internal</t>
   </si>
 </sst>
 </file>
@@ -1476,7 +1479,9 @@
       <c r="A59" t="s">
         <v>55</v>
       </c>
-      <c r="B59" s="1"/>
+      <c r="B59" s="1" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">

--- a/data/gravel/Tumbleweed Prospector 2025.xlsx
+++ b/data/gravel/Tumbleweed Prospector 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6995A89-8D60-3847-8999-659B965234CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B118B07-5395-174F-A726-69E44D1EF037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="122">
   <si>
     <t>brand</t>
   </si>
@@ -381,6 +381,24 @@
   </si>
   <si>
     <t>internal</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -750,7 +768,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K73"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1412,122 +1430,110 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>45</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>80</v>
+        <v>116</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>46</v>
+        <v>117</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>47</v>
-      </c>
-      <c r="B51">
-        <v>31.6</v>
+        <v>118</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>48</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>49</v>
+        <v>120</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>50</v>
+        <v>121</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>51</v>
-      </c>
-      <c r="B55">
-        <v>180</v>
+        <v>45</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>52</v>
-      </c>
-      <c r="B56">
-        <v>180</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>53</v>
+        <v>47</v>
+      </c>
+      <c r="B57">
+        <v>31.6</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>54</v>
+        <v>48</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>55</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>115</v>
+        <v>49</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>56</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>57</v>
+        <v>51</v>
+      </c>
+      <c r="B61">
+        <v>180</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>180</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>59</v>
-      </c>
-      <c r="B63">
-        <v>1</v>
+        <v>53</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>60</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>61</v>
+        <v>55</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>35</v>
@@ -1535,57 +1541,99 @@
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>63</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>64</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>35</v>
+        <v>58</v>
+      </c>
+      <c r="B68">
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B69">
-        <v>1550</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>66</v>
-      </c>
-      <c r="B70">
-        <v>4875</v>
+        <v>60</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>67</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
+        <v>62</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" t="s">
+        <v>63</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>64</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>65</v>
+      </c>
+      <c r="B75">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>66</v>
+      </c>
+      <c r="B76">
+        <v>4875</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>67</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
         <v>68</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B78" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
-      <c r="A73" s="1" t="s">
+    <row r="79" spans="1:2">
+      <c r="A79" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B79" s="1" t="s">
         <v>113</v>
       </c>
     </row>

--- a/data/gravel/Tumbleweed Prospector 2025.xlsx
+++ b/data/gravel/Tumbleweed Prospector 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B118B07-5395-174F-A726-69E44D1EF037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EA19815-C292-6D4D-95A2-4D24D3FCBFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="124">
   <si>
     <t>brand</t>
   </si>
@@ -365,9 +365,6 @@
     <t>steel</t>
   </si>
   <si>
-    <t>a8:f32</t>
-  </si>
-  <si>
     <t>https://tumbleweed.cc/cdn/shop/files/pros-award_23a5939b-1eba-42bb-babf-7ffab42be634.jpg?v=1756404856&amp;width=1000</t>
   </si>
   <si>
@@ -399,6 +396,15 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>a8:f34</t>
   </si>
 </sst>
 </file>
@@ -768,7 +774,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K79"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -816,7 +822,7 @@
     </row>
     <row r="6" spans="1:11">
       <c r="B6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="22">
@@ -824,7 +830,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="C7" s="3"/>
     </row>
@@ -1125,457 +1131,480 @@
       </c>
     </row>
     <row r="22" spans="1:7" ht="21">
-      <c r="A22" t="s">
-        <v>23</v>
+      <c r="A22" s="1" t="s">
+        <v>121</v>
       </c>
       <c r="B22" s="5"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="1"/>
+      <c r="C22" s="6">
+        <v>0</v>
+      </c>
+      <c r="D22" s="6">
+        <v>0</v>
+      </c>
+      <c r="E22" s="6">
+        <v>0</v>
+      </c>
+      <c r="F22" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="23" spans="1:7" ht="21">
       <c r="A23" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" s="6">
+        <v>0</v>
+      </c>
+      <c r="D23" s="6">
+        <v>0</v>
+      </c>
+      <c r="E23" s="6">
+        <v>0</v>
+      </c>
+      <c r="F23" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="21">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="5"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="1"/>
+    </row>
+    <row r="25" spans="1:7" ht="21">
+      <c r="A25" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B23" s="5"/>
-      <c r="G23" s="1"/>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" t="s">
-        <v>19</v>
-      </c>
-      <c r="G24" s="1"/>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" t="s">
-        <v>21</v>
-      </c>
+      <c r="B25" s="5"/>
       <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>22</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="G26" s="1"/>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>24</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="G27" s="1"/>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>26</v>
-      </c>
-      <c r="C28" s="1">
-        <v>650</v>
-      </c>
-      <c r="D28" s="1">
-        <v>650</v>
-      </c>
-      <c r="E28" s="1">
-        <v>650</v>
-      </c>
-      <c r="F28" s="1">
-        <v>650</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C30" s="1">
+        <v>650</v>
+      </c>
+      <c r="D30" s="1">
+        <v>650</v>
+      </c>
+      <c r="E30" s="1">
+        <v>650</v>
+      </c>
+      <c r="F30" s="1">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
         <v>27</v>
       </c>
-      <c r="C29">
+      <c r="C31">
         <f>2.8*25.4</f>
         <v>71.11999999999999</v>
       </c>
-      <c r="D29">
-        <f t="shared" ref="D29:F29" si="1">2.8*25.4</f>
+      <c r="D31">
+        <f t="shared" ref="D31:F31" si="1">2.8*25.4</f>
         <v>71.11999999999999</v>
       </c>
-      <c r="E29">
+      <c r="E31">
         <f t="shared" si="1"/>
         <v>71.11999999999999</v>
       </c>
-      <c r="F29">
+      <c r="F31">
         <f t="shared" si="1"/>
         <v>71.11999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
-      <c r="A30" t="s">
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
         <v>28</v>
       </c>
-      <c r="C30">
+      <c r="C32">
         <f>3*25.4</f>
         <v>76.199999999999989</v>
       </c>
-      <c r="D30">
-        <f t="shared" ref="D30:F30" si="2">3*25.4</f>
+      <c r="D32">
+        <f t="shared" ref="D32:F32" si="2">3*25.4</f>
         <v>76.199999999999989</v>
       </c>
-      <c r="E30">
+      <c r="E32">
         <f t="shared" si="2"/>
         <v>76.199999999999989</v>
       </c>
-      <c r="F30">
+      <c r="F32">
         <f t="shared" si="2"/>
         <v>76.199999999999989</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
-      <c r="A31" t="s">
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
         <v>29</v>
       </c>
-      <c r="C31">
-        <f>C33*2.54</f>
+      <c r="C33">
+        <f>C35*2.54</f>
         <v>157.47999999999999</v>
       </c>
-      <c r="D31">
-        <f>AVERAGE(D33,C34)*2.54</f>
+      <c r="D33">
+        <f>AVERAGE(D35,C36)*2.54</f>
         <v>168.91</v>
       </c>
-      <c r="E31">
-        <f t="shared" ref="E31:F31" si="3">AVERAGE(E33,D34)*2.54</f>
+      <c r="E33">
+        <f t="shared" ref="E33:F33" si="3">AVERAGE(E35,D36)*2.54</f>
         <v>177.8</v>
       </c>
-      <c r="F31">
+      <c r="F33">
         <f t="shared" si="3"/>
         <v>186.69</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
-      <c r="A32" t="s">
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
         <v>30</v>
       </c>
-      <c r="C32" s="1">
-        <f>D31</f>
+      <c r="C34" s="1">
+        <f>D33</f>
         <v>168.91</v>
       </c>
-      <c r="D32" s="1">
-        <f t="shared" ref="D32:E32" si="4">E31</f>
+      <c r="D34" s="1">
+        <f t="shared" ref="D34:E34" si="4">E33</f>
         <v>177.8</v>
       </c>
-      <c r="E32" s="1">
+      <c r="E34" s="1">
         <f t="shared" si="4"/>
         <v>186.69</v>
       </c>
-      <c r="F32">
-        <f t="shared" ref="F32" si="5">F34*2.54</f>
+      <c r="F34">
+        <f t="shared" ref="F34" si="5">F36*2.54</f>
         <v>200.66</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
-      <c r="C33">
+    <row r="35" spans="1:7">
+      <c r="C35">
         <v>62</v>
       </c>
-      <c r="D33">
+      <c r="D35">
         <v>66</v>
       </c>
-      <c r="E33">
+      <c r="E35">
         <v>70</v>
       </c>
-      <c r="F33">
+      <c r="F35">
         <v>73</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
-      <c r="A34" t="s">
+    <row r="36" spans="1:7">
+      <c r="A36" t="s">
         <v>31</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B36" t="s">
         <v>32</v>
       </c>
-      <c r="C34">
+      <c r="C36">
         <v>67</v>
       </c>
-      <c r="D34">
+      <c r="D36">
         <v>70</v>
       </c>
-      <c r="E34">
+      <c r="E36">
         <v>74</v>
       </c>
-      <c r="F34">
+      <c r="F36">
         <v>79</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="21">
-      <c r="A35" t="s">
+    <row r="37" spans="1:7" ht="21">
+      <c r="A37" t="s">
         <v>69</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B37" t="s">
         <v>70</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C37" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D37" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="E37" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="F35" s="6" t="s">
+      <c r="F37" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="G35" s="5" t="s">
+      <c r="G37" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="21">
-      <c r="A36" t="s">
+    <row r="38" spans="1:7" ht="21">
+      <c r="A38" t="s">
         <v>71</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B38" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C38" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="D36" s="6" t="s">
+      <c r="D38" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="E36" s="6" t="s">
+      <c r="E38" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="F36" s="6" t="s">
+      <c r="F38" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="G36" s="5" t="s">
+      <c r="G38" s="5" t="s">
         <v>107</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37" t="s">
-        <v>72</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38" t="s">
-        <v>33</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>34</v>
+        <v>72</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>36</v>
+        <v>33</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" t="s">
         <v>37</v>
       </c>
-      <c r="B41">
+      <c r="B43">
         <f>3*25.4</f>
         <v>76.199999999999989</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
-      <c r="A42" t="s">
-        <v>38</v>
-      </c>
-      <c r="B42">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43" t="s">
-        <v>39</v>
-      </c>
-      <c r="B43">
-        <v>100</v>
-      </c>
-    </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>40</v>
-      </c>
-      <c r="B44" s="1"/>
+        <v>38</v>
+      </c>
+      <c r="B44">
+        <v>3.8</v>
+      </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>39</v>
+      </c>
+      <c r="B45">
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>42</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="B46" s="1"/>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>43</v>
-      </c>
-      <c r="B47">
-        <v>148</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>44</v>
-      </c>
-      <c r="B48">
-        <v>110</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>116</v>
+        <v>43</v>
+      </c>
+      <c r="B49">
+        <v>148</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>117</v>
+        <v>44</v>
+      </c>
+      <c r="B50">
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>45</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>46</v>
+        <v>120</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>47</v>
-      </c>
-      <c r="B57">
-        <v>31.6</v>
+        <v>45</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>48</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>49</v>
+        <v>47</v>
+      </c>
+      <c r="B59">
+        <v>31.6</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>50</v>
+        <v>48</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>51</v>
-      </c>
-      <c r="B61">
-        <v>180</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>52</v>
-      </c>
-      <c r="B62">
-        <v>180</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>53</v>
+        <v>51</v>
+      </c>
+      <c r="B63">
+        <v>180</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>54</v>
+        <v>52</v>
+      </c>
+      <c r="B64">
+        <v>180</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>55</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>115</v>
+        <v>53</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>56</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>57</v>
+        <v>55</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>58</v>
-      </c>
-      <c r="B68">
-        <v>2</v>
+        <v>56</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>59</v>
-      </c>
-      <c r="B69">
-        <v>1</v>
+        <v>57</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>60</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>35</v>
+        <v>58</v>
+      </c>
+      <c r="B70">
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>61</v>
+        <v>59</v>
+      </c>
+      <c r="B71">
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>35</v>
@@ -1583,15 +1612,12 @@
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>63</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>35</v>
@@ -1599,42 +1625,58 @@
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>65</v>
-      </c>
-      <c r="B75">
-        <v>1550</v>
+        <v>63</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>66</v>
-      </c>
-      <c r="B76">
-        <v>4875</v>
+        <v>64</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>67</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>35</v>
+        <v>65</v>
+      </c>
+      <c r="B77">
+        <v>1550</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
+        <v>66</v>
+      </c>
+      <c r="B78">
+        <v>4875</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>67</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
         <v>68</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2">
-      <c r="A79" s="1" t="s">
+      <c r="B80" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>113</v>
       </c>
     </row>
   </sheetData>
